--- a/Files/Preregistrations/gspaceuse_ResultsTables.xlsx
+++ b/Files/Preregistrations/gspaceuse_ResultsTables.xlsx
@@ -5,17 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelseymccune/Documents/Grackle project/Space use/Space Use Workflow/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelseymccune/Documents/GitHub/grackles/Files/Preregistrations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84EC0C69-3CA9-2F4C-A48A-25D3F1037CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5C91C3-77BF-7D47-B7D9-1BC42DAA663A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" activeTab="2" xr2:uid="{AF51339F-4806-8849-890B-6E5356CC2B1D}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18800" activeTab="1" xr2:uid="{AF51339F-4806-8849-890B-6E5356CC2B1D}"/>
   </bookViews>
   <sheets>
     <sheet name="Table_H1" sheetId="1" r:id="rId1"/>
-    <sheet name="Table_HR" sheetId="2" r:id="rId2"/>
-    <sheet name="Table_H2" sheetId="3" r:id="rId3"/>
+    <sheet name="Table_H2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="24">
   <si>
     <t>Arizona</t>
   </si>
@@ -62,15 +61,6 @@
   </si>
   <si>
     <t>UCL</t>
-  </si>
-  <si>
-    <t>effective sample size</t>
-  </si>
-  <si>
-    <t>posterior mean</t>
-  </si>
-  <si>
-    <t>p-value</t>
   </si>
   <si>
     <t>Season (Breeding)</t>
@@ -662,23 +652,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -749,9 +734,6 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1146,86 +1128,86 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" ht="22" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="14"/>
-      <c r="T2" s="14"/>
-      <c r="U2" s="14"/>
-      <c r="V2" s="14"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
     </row>
     <row r="3" spans="2:22" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="L3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="O3" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="P3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="Q3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="R3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="O3" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="R3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="S3" s="6"/>
+      <c r="S3" s="5"/>
     </row>
     <row r="4" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="35"/>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="32"/>
       <c r="D4" s="2">
         <v>-0.16330900000000001</v>
       </c>
@@ -1235,7 +1217,7 @@
       <c r="F4" s="2">
         <v>0.66291199999999995</v>
       </c>
-      <c r="G4" s="31"/>
+      <c r="G4" s="28"/>
       <c r="H4">
         <v>-0.15</v>
       </c>
@@ -1245,7 +1227,7 @@
       <c r="J4">
         <v>0.3256</v>
       </c>
-      <c r="K4" s="31"/>
+      <c r="K4" s="28"/>
       <c r="L4">
         <v>0.02</v>
       </c>
@@ -1255,7 +1237,7 @@
       <c r="N4" s="2">
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="O4" s="31"/>
+      <c r="O4" s="28"/>
       <c r="P4" s="2">
         <v>0.45362011857288798</v>
       </c>
@@ -1267,10 +1249,10 @@
       </c>
     </row>
     <row r="5" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="35"/>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="32"/>
       <c r="D5" s="2">
         <v>0.72434600000000005</v>
       </c>
@@ -1280,7 +1262,7 @@
       <c r="F5" s="2">
         <v>1.6667620000000001</v>
       </c>
-      <c r="G5" s="31"/>
+      <c r="G5" s="28"/>
       <c r="H5">
         <v>0.09</v>
       </c>
@@ -1290,7 +1272,7 @@
       <c r="J5">
         <v>0.35519999999999996</v>
       </c>
-      <c r="K5" s="31"/>
+      <c r="K5" s="28"/>
       <c r="L5">
         <v>0</v>
       </c>
@@ -1300,7 +1282,7 @@
       <c r="N5" s="2">
         <v>7.8399999999999997E-2</v>
       </c>
-      <c r="O5" s="31"/>
+      <c r="O5" s="28"/>
       <c r="P5" s="2">
         <v>-0.42120986749230199</v>
       </c>
@@ -1312,10 +1294,10 @@
       </c>
     </row>
     <row r="6" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="35"/>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="32"/>
       <c r="D6" s="2">
         <v>-0.34717500000000001</v>
       </c>
@@ -1325,7 +1307,7 @@
       <c r="F6" s="2">
         <v>3.4334039999999999</v>
       </c>
-      <c r="G6" s="31"/>
+      <c r="G6" s="28"/>
       <c r="H6">
         <v>-0.23</v>
       </c>
@@ -1335,7 +1317,7 @@
       <c r="J6">
         <v>0.91759999999999997</v>
       </c>
-      <c r="K6" s="31"/>
+      <c r="K6" s="28"/>
       <c r="L6">
         <v>0.04</v>
       </c>
@@ -1345,7 +1327,7 @@
       <c r="N6" s="2">
         <v>0.2752</v>
       </c>
-      <c r="O6" s="31"/>
+      <c r="O6" s="28"/>
       <c r="P6" s="2">
         <v>0.40246058223497599</v>
       </c>
@@ -1357,10 +1339,10 @@
       </c>
     </row>
     <row r="7" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="35"/>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="32"/>
       <c r="D7" s="2">
         <v>1.226E-2</v>
       </c>
@@ -1370,7 +1352,7 @@
       <c r="F7" s="2">
         <v>2.6022E-2</v>
       </c>
-      <c r="G7" s="31"/>
+      <c r="G7" s="28"/>
       <c r="H7">
         <v>0.1</v>
       </c>
@@ -1380,7 +1362,7 @@
       <c r="J7">
         <v>0.3256</v>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="28"/>
       <c r="L7">
         <v>0.04</v>
       </c>
@@ -1390,7 +1372,7 @@
       <c r="N7" s="2">
         <v>0.11840000000000001</v>
       </c>
-      <c r="O7" s="31"/>
+      <c r="O7" s="28"/>
       <c r="P7" s="2">
         <v>-3.1150758588465E-2</v>
       </c>
@@ -1402,10 +1384,10 @@
       </c>
     </row>
     <row r="8" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="35"/>
+      <c r="C8" s="32"/>
       <c r="D8" s="2">
         <v>0.10616</v>
       </c>
@@ -1415,7 +1397,7 @@
       <c r="F8" s="2">
         <v>0.30156300000000003</v>
       </c>
-      <c r="G8" s="31"/>
+      <c r="G8" s="28"/>
       <c r="H8" s="1">
         <v>0.36</v>
       </c>
@@ -1425,17 +1407,17 @@
       <c r="J8" s="1">
         <v>0.23680000000000001</v>
       </c>
-      <c r="K8" s="31"/>
+      <c r="K8" s="28"/>
       <c r="L8" s="1">
         <v>-0.1</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="9">
         <v>-0.1784</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="9">
         <v>-2.1600000000000008E-2</v>
       </c>
-      <c r="O8" s="31"/>
+      <c r="O8" s="28"/>
       <c r="P8" s="2">
         <v>-0.44016923637883798</v>
       </c>
@@ -1447,10 +1429,10 @@
       </c>
     </row>
     <row r="9" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="35"/>
+      <c r="C9" s="32"/>
       <c r="D9" s="2">
         <v>-6.5300000000000002E-3</v>
       </c>
@@ -1460,7 +1442,7 @@
       <c r="F9" s="2">
         <v>0.18703400000000001</v>
       </c>
-      <c r="G9" s="31"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="1">
         <v>0.36</v>
       </c>
@@ -1470,32 +1452,32 @@
       <c r="J9" s="1">
         <v>0.23680000000000001</v>
       </c>
-      <c r="K9" s="31"/>
+      <c r="K9" s="28"/>
       <c r="L9" s="1">
         <v>-0.13</v>
       </c>
-      <c r="M9" s="12">
+      <c r="M9" s="9">
         <v>-0.1888</v>
       </c>
-      <c r="N9" s="12">
+      <c r="N9" s="9">
         <v>-7.1200000000000013E-2</v>
       </c>
-      <c r="O9" s="31"/>
-      <c r="P9" s="12">
+      <c r="O9" s="28"/>
+      <c r="P9" s="9">
         <v>-0.74048067435148501</v>
       </c>
-      <c r="Q9" s="12">
+      <c r="Q9" s="9">
         <v>-1.2553903763744101</v>
       </c>
-      <c r="R9" s="12">
+      <c r="R9" s="9">
         <v>-0.23950885741175401</v>
       </c>
     </row>
     <row r="10" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="35"/>
+      <c r="C10" s="32"/>
       <c r="D10" s="2">
         <v>0.166966</v>
       </c>
@@ -1505,7 +1487,7 @@
       <c r="F10" s="2">
         <v>0.60087199999999996</v>
       </c>
-      <c r="G10" s="31"/>
+      <c r="G10" s="28"/>
       <c r="H10">
         <v>-0.09</v>
       </c>
@@ -1515,7 +1497,7 @@
       <c r="J10">
         <v>0.35519999999999996</v>
       </c>
-      <c r="K10" s="31"/>
+      <c r="K10" s="28"/>
       <c r="L10">
         <v>0.05</v>
       </c>
@@ -1525,7 +1507,7 @@
       <c r="N10" s="2">
         <v>0.12840000000000001</v>
       </c>
-      <c r="O10" s="31"/>
+      <c r="O10" s="28"/>
       <c r="P10" s="2">
         <v>0.173843210164873</v>
       </c>
@@ -1537,10 +1519,10 @@
       </c>
     </row>
     <row r="11" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="32"/>
       <c r="D11" s="2">
         <v>9.4459999999999995E-3</v>
       </c>
@@ -1550,7 +1532,7 @@
       <c r="F11" s="2">
         <v>6.6406000000000007E-2</v>
       </c>
-      <c r="G11" s="31"/>
+      <c r="G11" s="28"/>
       <c r="H11">
         <v>0.1</v>
       </c>
@@ -1560,7 +1542,7 @@
       <c r="J11">
         <v>0.3256</v>
       </c>
-      <c r="K11" s="31"/>
+      <c r="K11" s="28"/>
       <c r="L11">
         <v>0</v>
       </c>
@@ -1570,7 +1552,7 @@
       <c r="N11" s="2">
         <v>7.8399999999999997E-2</v>
       </c>
-      <c r="O11" s="31"/>
+      <c r="O11" s="28"/>
       <c r="P11" s="2">
         <v>-0.141058935161124</v>
       </c>
@@ -1582,10 +1564,10 @@
       </c>
     </row>
     <row r="12" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="35"/>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="32"/>
       <c r="D12" s="2">
         <v>0.55755600000000005</v>
       </c>
@@ -1595,7 +1577,7 @@
       <c r="F12" s="2">
         <v>2.3044959999999999</v>
       </c>
-      <c r="G12" s="31"/>
+      <c r="G12" s="28"/>
       <c r="H12">
         <v>0.03</v>
       </c>
@@ -1605,7 +1587,7 @@
       <c r="J12">
         <v>0.74</v>
       </c>
-      <c r="K12" s="31"/>
+      <c r="K12" s="28"/>
       <c r="L12">
         <v>-0.09</v>
       </c>
@@ -1615,7 +1597,7 @@
       <c r="N12" s="2">
         <v>8.6400000000000005E-2</v>
       </c>
-      <c r="O12" s="31"/>
+      <c r="O12" s="28"/>
       <c r="P12" s="2">
         <v>2.65817041929748E-2</v>
       </c>
@@ -1627,95 +1609,95 @@
       </c>
     </row>
     <row r="13" spans="2:22" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="15"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="16"/>
-      <c r="K13" s="16"/>
-      <c r="O13" s="17"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="O13" s="14"/>
     </row>
     <row r="14" spans="2:22" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="33"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="33"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="14"/>
-      <c r="U14" s="14"/>
-      <c r="V14" s="14"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="30"/>
+      <c r="L14" s="30"/>
+      <c r="M14" s="30"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="30"/>
+      <c r="P14" s="30"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="11"/>
     </row>
     <row r="15" spans="2:22" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C15" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="C15" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K15" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="O15" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="P15" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I15" s="6" t="s">
+      <c r="Q15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="R15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="P15" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="R15" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="S15" s="6"/>
+      <c r="S15" s="5"/>
     </row>
     <row r="16" spans="2:22" ht="19" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="35"/>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="32"/>
       <c r="D16" s="2">
         <v>-0.28937800000000002</v>
       </c>
@@ -1725,7 +1707,7 @@
       <c r="F16" s="2">
         <v>1.6384590000000001</v>
       </c>
-      <c r="G16" s="31"/>
+      <c r="G16" s="28"/>
       <c r="H16">
         <v>-0.11</v>
       </c>
@@ -1735,7 +1717,7 @@
       <c r="J16" s="2">
         <v>2.7200000000000016E-2</v>
       </c>
-      <c r="K16" s="31"/>
+      <c r="K16" s="28"/>
       <c r="L16">
         <v>-0.05</v>
       </c>
@@ -1745,7 +1727,7 @@
       <c r="N16" s="2">
         <v>2.8399999999999995E-2</v>
       </c>
-      <c r="O16" s="31"/>
+      <c r="O16" s="28"/>
       <c r="P16" s="2">
         <v>-0.53996917817199996</v>
       </c>
@@ -1757,10 +1739,10 @@
       </c>
     </row>
     <row r="17" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="35"/>
+      <c r="B17" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="32"/>
       <c r="D17" s="2">
         <v>0.46058300000000002</v>
       </c>
@@ -1770,7 +1752,7 @@
       <c r="F17" s="2">
         <v>2.281304</v>
       </c>
-      <c r="G17" s="31"/>
+      <c r="G17" s="28"/>
       <c r="H17">
         <v>0.04</v>
       </c>
@@ -1780,7 +1762,7 @@
       <c r="J17" s="2">
         <v>0.17720000000000002</v>
       </c>
-      <c r="K17" s="31"/>
+      <c r="K17" s="28"/>
       <c r="L17">
         <v>0.01</v>
       </c>
@@ -1790,7 +1772,7 @@
       <c r="N17" s="2">
         <v>8.8399999999999992E-2</v>
       </c>
-      <c r="O17" s="31"/>
+      <c r="O17" s="28"/>
       <c r="P17" s="2">
         <v>0.43226182881000003</v>
       </c>
@@ -1802,10 +1784,10 @@
       </c>
     </row>
     <row r="18" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="35"/>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="32"/>
       <c r="D18" s="2">
         <v>6.9281999999999996E-2</v>
       </c>
@@ -1815,7 +1797,7 @@
       <c r="F18" s="2">
         <v>11.319285000000001</v>
       </c>
-      <c r="G18" s="31"/>
+      <c r="G18" s="28"/>
       <c r="H18">
         <v>0.06</v>
       </c>
@@ -1825,7 +1807,7 @@
       <c r="J18" s="2">
         <v>0.35399999999999998</v>
       </c>
-      <c r="K18" s="31"/>
+      <c r="K18" s="28"/>
       <c r="L18">
         <v>-0.05</v>
       </c>
@@ -1835,7 +1817,7 @@
       <c r="N18" s="2">
         <v>0.12640000000000001</v>
       </c>
-      <c r="O18" s="31"/>
+      <c r="O18" s="28"/>
       <c r="P18" s="2">
         <v>-0.85219150236899999</v>
       </c>
@@ -1847,10 +1829,10 @@
       </c>
     </row>
     <row r="19" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="35"/>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="32"/>
       <c r="D19" s="2">
         <v>4.6267000000000003E-2</v>
       </c>
@@ -1860,7 +1842,7 @@
       <c r="F19" s="2">
         <v>0.154668</v>
       </c>
-      <c r="G19" s="31"/>
+      <c r="G19" s="28"/>
       <c r="H19">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -1870,7 +1852,7 @@
       <c r="J19" s="2">
         <v>0.20720000000000002</v>
       </c>
-      <c r="K19" s="31"/>
+      <c r="K19" s="28"/>
       <c r="L19">
         <v>-0.02</v>
       </c>
@@ -1880,7 +1862,7 @@
       <c r="N19" s="2">
         <v>5.8399999999999994E-2</v>
       </c>
-      <c r="O19" s="31"/>
+      <c r="O19" s="28"/>
       <c r="P19" s="2">
         <v>-0.35842666133700002</v>
       </c>
@@ -1892,10 +1874,10 @@
       </c>
     </row>
     <row r="20" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="35"/>
+      <c r="C20" s="32"/>
       <c r="D20" s="2">
         <v>0.33827600000000002</v>
       </c>
@@ -1905,7 +1887,7 @@
       <c r="F20" s="2">
         <v>1.2500819999999999</v>
       </c>
-      <c r="G20" s="31"/>
+      <c r="G20" s="28"/>
       <c r="H20">
         <v>7.0000000000000007E-2</v>
       </c>
@@ -1915,7 +1897,7 @@
       <c r="J20" s="2">
         <v>0.20720000000000002</v>
       </c>
-      <c r="K20" s="31"/>
+      <c r="K20" s="28"/>
       <c r="L20">
         <v>-0.01</v>
       </c>
@@ -1925,7 +1907,7 @@
       <c r="N20" s="2">
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="O20" s="31"/>
+      <c r="O20" s="28"/>
       <c r="P20" s="2">
         <v>-0.178095209005</v>
       </c>
@@ -1937,10 +1919,10 @@
       </c>
     </row>
     <row r="21" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C21" s="35"/>
+      <c r="C21" s="32"/>
       <c r="D21" s="2">
         <v>2.5269E-2</v>
       </c>
@@ -1950,7 +1932,7 @@
       <c r="F21" s="2">
         <v>0.15618799999999999</v>
       </c>
-      <c r="G21" s="31"/>
+      <c r="G21" s="28"/>
       <c r="H21">
         <v>0.1</v>
       </c>
@@ -1960,7 +1942,7 @@
       <c r="J21" s="2">
         <v>0.23720000000000002</v>
       </c>
-      <c r="K21" s="31"/>
+      <c r="K21" s="28"/>
       <c r="L21">
         <v>0.08</v>
       </c>
@@ -1970,7 +1952,7 @@
       <c r="N21" s="2">
         <v>0.15839999999999999</v>
       </c>
-      <c r="O21" s="31"/>
+      <c r="O21" s="28"/>
       <c r="P21" s="2">
         <v>0.14330219574950001</v>
       </c>
@@ -1982,10 +1964,10 @@
       </c>
     </row>
     <row r="22" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C22" s="35"/>
+      <c r="C22" s="32"/>
       <c r="D22" s="2">
         <v>-0.17435400000000001</v>
       </c>
@@ -1995,7 +1977,7 @@
       <c r="F22" s="2">
         <v>0.56671099999999996</v>
       </c>
-      <c r="G22" s="31"/>
+      <c r="G22" s="28"/>
       <c r="H22">
         <v>-0.02</v>
       </c>
@@ -2005,7 +1987,7 @@
       <c r="J22" s="2">
         <v>0.11720000000000001</v>
       </c>
-      <c r="K22" s="31"/>
+      <c r="K22" s="28"/>
       <c r="L22">
         <v>-0.05</v>
       </c>
@@ -2015,7 +1997,7 @@
       <c r="N22" s="2">
         <v>2.8399999999999995E-2</v>
       </c>
-      <c r="O22" s="31"/>
+      <c r="O22" s="28"/>
       <c r="P22" s="2">
         <v>-0.66351275332199999</v>
       </c>
@@ -2027,10 +2009,10 @@
       </c>
     </row>
     <row r="23" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C23" s="35"/>
+      <c r="C23" s="32"/>
       <c r="D23" s="2">
         <v>4.4619999999999998E-3</v>
       </c>
@@ -2040,7 +2022,7 @@
       <c r="F23" s="2">
         <v>0.18478800000000001</v>
       </c>
-      <c r="G23" s="31"/>
+      <c r="G23" s="28"/>
       <c r="H23">
         <v>-0.04</v>
       </c>
@@ -2050,7 +2032,7 @@
       <c r="J23" s="2">
         <v>9.7200000000000009E-2</v>
       </c>
-      <c r="K23" s="31"/>
+      <c r="K23" s="28"/>
       <c r="L23">
         <v>0.02</v>
       </c>
@@ -2060,7 +2042,7 @@
       <c r="N23" s="2">
         <v>9.8400000000000001E-2</v>
       </c>
-      <c r="O23" s="31"/>
+      <c r="O23" s="28"/>
       <c r="P23" s="2">
         <v>0.39710398642020001</v>
       </c>
@@ -2072,20 +2054,20 @@
       </c>
     </row>
     <row r="24" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B24" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="36"/>
-      <c r="D24" s="10">
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="8">
         <v>2.317097</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="8">
         <v>-3.3415439999999998</v>
       </c>
-      <c r="F24" s="10">
+      <c r="F24" s="8">
         <v>8.1113320000000009</v>
       </c>
-      <c r="G24" s="31"/>
+      <c r="G24" s="28"/>
       <c r="H24">
         <v>-0.1</v>
       </c>
@@ -2095,7 +2077,7 @@
       <c r="J24" s="2">
         <v>0.19399999999999998</v>
       </c>
-      <c r="K24" s="31"/>
+      <c r="K24" s="28"/>
       <c r="L24">
         <v>0.09</v>
       </c>
@@ -2105,34 +2087,34 @@
       <c r="N24" s="2">
         <v>0.26639999999999997</v>
       </c>
-      <c r="O24" s="32"/>
-      <c r="P24" s="10">
+      <c r="O24" s="29"/>
+      <c r="P24" s="8">
         <v>0.43340814735700001</v>
       </c>
-      <c r="Q24" s="10">
+      <c r="Q24" s="8">
         <v>-0.88772068500000001</v>
       </c>
-      <c r="R24" s="10">
+      <c r="R24" s="8">
         <v>1.7454863</v>
       </c>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -2153,447 +2135,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDBFBDBE-C763-4947-9AF7-119F5960FD7C}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:G23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" customWidth="1"/>
-    <col min="6" max="6" width="14.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="B2" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-    </row>
-    <row r="3" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2"/>
-      <c r="C3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-0.16330900000000001</v>
-      </c>
-      <c r="D4" s="2">
-        <v>-0.99076900000000001</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0.66291199999999995</v>
-      </c>
-      <c r="F4" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.66739999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="2">
-        <v>0.72434600000000005</v>
-      </c>
-      <c r="D5" s="2">
-        <v>-0.25037300000000001</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1.6667620000000001</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.13700000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-0.34717500000000001</v>
-      </c>
-      <c r="D6" s="2">
-        <v>-4.5758619999999999</v>
-      </c>
-      <c r="E6" s="2">
-        <v>3.4334039999999999</v>
-      </c>
-      <c r="F6" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.8478</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1.226E-2</v>
-      </c>
-      <c r="D7" s="2">
-        <v>-9.9799999999999997E-4</v>
-      </c>
-      <c r="E7" s="2">
-        <v>2.6022E-2</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G7" s="2">
-        <v>6.9599999999999995E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2">
-        <v>0.10616</v>
-      </c>
-      <c r="D8" s="2">
-        <v>-8.5430000000000006E-2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>0.30156300000000003</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G8" s="2">
-        <v>0.2576</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="2">
-        <v>-6.5300000000000002E-3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>-0.19955100000000001</v>
-      </c>
-      <c r="E9" s="2">
-        <v>0.18703400000000001</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G9" s="2">
-        <v>0.9304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2">
-        <v>0.166966</v>
-      </c>
-      <c r="D10" s="2">
-        <v>-0.19483800000000001</v>
-      </c>
-      <c r="E10" s="2">
-        <v>0.60087199999999996</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G10" s="2">
-        <v>0.38590000000000002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="2">
-        <v>9.4459999999999995E-3</v>
-      </c>
-      <c r="D11" s="2">
-        <v>-4.0335000000000003E-2</v>
-      </c>
-      <c r="E11" s="2">
-        <v>6.6406000000000007E-2</v>
-      </c>
-      <c r="F11" s="3">
-        <v>1840</v>
-      </c>
-      <c r="G11" s="2">
-        <v>0.68799999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B12" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="10">
-        <v>0.55755600000000005</v>
-      </c>
-      <c r="D12" s="10">
-        <v>-1.21641</v>
-      </c>
-      <c r="E12" s="10">
-        <v>2.3044959999999999</v>
-      </c>
-      <c r="F12" s="11">
-        <v>1840</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0.48259999999999997</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="22" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-    </row>
-    <row r="14" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2">
-        <v>-0.28937800000000002</v>
-      </c>
-      <c r="D15" s="2">
-        <v>-2.3254329999999999</v>
-      </c>
-      <c r="E15" s="2">
-        <v>1.6384590000000001</v>
-      </c>
-      <c r="F15" s="3">
-        <v>4335</v>
-      </c>
-      <c r="G15" s="2">
-        <v>0.75800000000000001</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" s="2">
-        <v>0.46058300000000002</v>
-      </c>
-      <c r="D16" s="2">
-        <v>-1.4425460000000001</v>
-      </c>
-      <c r="E16" s="2">
-        <v>2.281304</v>
-      </c>
-      <c r="F16" s="3">
-        <v>3840</v>
-      </c>
-      <c r="G16" s="2">
-        <v>0.60699999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="2">
-        <v>6.9281999999999996E-2</v>
-      </c>
-      <c r="D17" s="2">
-        <v>-11.294397999999999</v>
-      </c>
-      <c r="E17" s="2">
-        <v>11.319285000000001</v>
-      </c>
-      <c r="F17" s="3">
-        <v>3840</v>
-      </c>
-      <c r="G17" s="2">
-        <v>0.99299999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <v>4.6267000000000003E-2</v>
-      </c>
-      <c r="D18" s="2">
-        <v>-6.4208000000000001E-2</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0.154668</v>
-      </c>
-      <c r="F18" s="3">
-        <v>3840</v>
-      </c>
-      <c r="G18" s="2">
-        <v>0.38600000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0.33827600000000002</v>
-      </c>
-      <c r="D19" s="2">
-        <v>-0.47237800000000002</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1.2500819999999999</v>
-      </c>
-      <c r="F19" s="3">
-        <v>3840</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.40300000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2">
-        <v>2.5269E-2</v>
-      </c>
-      <c r="D20" s="2">
-        <v>-0.109503</v>
-      </c>
-      <c r="E20" s="2">
-        <v>0.15618799999999999</v>
-      </c>
-      <c r="F20" s="3">
-        <v>3638</v>
-      </c>
-      <c r="G20" s="2">
-        <v>0.68700000000000006</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
-        <v>-0.17435400000000001</v>
-      </c>
-      <c r="D21" s="2">
-        <v>-0.934307</v>
-      </c>
-      <c r="E21" s="2">
-        <v>0.56671099999999996</v>
-      </c>
-      <c r="F21" s="3">
-        <v>3565</v>
-      </c>
-      <c r="G21" s="2">
-        <v>0.627</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B22" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="2">
-        <v>4.4619999999999998E-3</v>
-      </c>
-      <c r="D22" s="2">
-        <v>-0.155889</v>
-      </c>
-      <c r="E22" s="2">
-        <v>0.18478800000000001</v>
-      </c>
-      <c r="F22" s="3">
-        <v>3840</v>
-      </c>
-      <c r="G22" s="2">
-        <v>0.94899999999999995</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" ht="19" x14ac:dyDescent="0.25">
-      <c r="B23" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="10">
-        <v>2.317097</v>
-      </c>
-      <c r="D23" s="10">
-        <v>-3.3415439999999998</v>
-      </c>
-      <c r="E23" s="10">
-        <v>8.1113320000000009</v>
-      </c>
-      <c r="F23" s="11">
-        <v>3354</v>
-      </c>
-      <c r="G23" s="10">
-        <v>0.40799999999999997</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B13:G13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="95" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57A01CC6-32D1-6E4E-8752-A1C5994F1E3C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -2603,78 +2144,78 @@
   <cols>
     <col min="1" max="1" width="27.5" customWidth="1"/>
     <col min="2" max="2" width="18.1640625" customWidth="1"/>
-    <col min="4" max="5" width="10.83203125" style="25"/>
-    <col min="6" max="6" width="10" style="21" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="25" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" style="25"/>
-    <col min="10" max="10" width="9.6640625" style="21" customWidth="1"/>
-    <col min="12" max="13" width="10.83203125" style="25"/>
+    <col min="4" max="5" width="10.83203125" style="22"/>
+    <col min="6" max="6" width="10" style="18" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="22" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="22"/>
+    <col min="10" max="10" width="9.6640625" style="18" customWidth="1"/>
+    <col min="12" max="13" width="10.83203125" style="22"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
-    <col min="16" max="17" width="10.83203125" style="25"/>
-    <col min="18" max="18" width="9.1640625" style="21" customWidth="1"/>
+    <col min="16" max="17" width="10.83203125" style="22"/>
+    <col min="18" max="18" width="9.1640625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:18" ht="40" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19"/>
-      <c r="C3" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
     </row>
     <row r="4" spans="2:18" ht="19" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J4" s="22" t="s">
+      <c r="J4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="22" t="s">
+      <c r="K4" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="N4" s="22" t="s">
+      <c r="N4" s="19" t="s">
         <v>8</v>
       </c>
       <c r="P4"/>
@@ -2682,43 +2223,43 @@
       <c r="R4"/>
     </row>
     <row r="5" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="12">
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="9">
         <v>3.48</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="25">
         <v>1.62</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="25">
         <v>5.31</v>
       </c>
       <c r="F5" s="1">
         <v>-0.77</v>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="24">
         <v>-1.06</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="24">
         <v>-0.49</v>
       </c>
       <c r="I5">
         <v>-0.02</v>
       </c>
-      <c r="J5" s="23">
+      <c r="J5" s="20">
         <v>-0.15</v>
       </c>
-      <c r="K5" s="23">
+      <c r="K5" s="20">
         <v>0.12</v>
       </c>
       <c r="L5" s="2">
         <v>-0.04</v>
       </c>
-      <c r="M5" s="23">
+      <c r="M5" s="20">
         <v>-1.57</v>
       </c>
-      <c r="N5" s="23">
+      <c r="N5" s="20">
         <v>1.65</v>
       </c>
       <c r="P5"/>
@@ -2726,43 +2267,43 @@
       <c r="R5"/>
     </row>
     <row r="6" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
-        <v>13</v>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C6" s="2">
         <v>0.11</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="20">
         <v>-1.54</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="20">
         <v>1.71</v>
       </c>
       <c r="F6">
         <v>-0.01</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="22">
         <v>-0.28999999999999998</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="22">
         <v>0.31</v>
       </c>
       <c r="I6">
         <v>-0.02</v>
       </c>
-      <c r="J6" s="23">
+      <c r="J6" s="20">
         <v>-0.17</v>
       </c>
-      <c r="K6" s="23">
+      <c r="K6" s="20">
         <v>0.12</v>
       </c>
       <c r="L6" s="2">
         <v>-0.48</v>
       </c>
-      <c r="M6" s="23">
+      <c r="M6" s="20">
         <v>-1.87</v>
       </c>
-      <c r="N6" s="23">
+      <c r="N6" s="20">
         <v>0.85</v>
       </c>
       <c r="P6"/>
@@ -2770,43 +2311,43 @@
       <c r="R6"/>
     </row>
     <row r="7" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
-        <v>14</v>
+      <c r="B7" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="C7" s="2">
         <v>0.02</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="20">
         <v>0</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="20">
         <v>0.03</v>
       </c>
       <c r="F7">
         <v>0.1</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="22">
         <v>-0.05</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="22">
         <v>0.25</v>
       </c>
       <c r="I7">
         <v>0.01</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="20">
         <v>-0.06</v>
       </c>
-      <c r="K7" s="23">
+      <c r="K7" s="20">
         <v>0.09</v>
       </c>
       <c r="L7" s="2">
         <v>0</v>
       </c>
-      <c r="M7" s="23">
+      <c r="M7" s="20">
         <v>-0.01</v>
       </c>
-      <c r="N7" s="23">
+      <c r="N7" s="20">
         <v>0.02</v>
       </c>
       <c r="P7"/>
@@ -2814,43 +2355,43 @@
       <c r="R7"/>
     </row>
     <row r="8" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B8" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="10">
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="8">
         <v>0.96</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="21">
         <v>-0.72</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="21">
         <v>2.86</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="15">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="23">
         <v>-0.28999999999999998</v>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="23">
         <v>0.43</v>
       </c>
-      <c r="I8" s="18">
+      <c r="I8" s="15">
         <v>0.02</v>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="21">
         <v>-0.17</v>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="21">
         <v>0.17</v>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="8">
         <v>-0.77</v>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="21">
         <v>-2.16</v>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="21">
         <v>0.72</v>
       </c>
       <c r="P8"/>
@@ -2858,81 +2399,81 @@
       <c r="R8"/>
     </row>
     <row r="9" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B9" s="7"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="17"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="20"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="17"/>
       <c r="K9" s="1"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="16"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="13"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="23"/>
-      <c r="Q9" s="23"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
     </row>
     <row r="10" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
+      <c r="B10" s="6"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="17"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="20"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="17"/>
       <c r="K10" s="1"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="12"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="28"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
     </row>
     <row r="11" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B11" s="4"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="16"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="17"/>
+      <c r="J11" s="17"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="13"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="23"/>
-      <c r="Q11" s="23"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
     </row>
     <row r="12" spans="2:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="B12" s="4"/>
+      <c r="B12" s="3"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="L12" s="23"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="16"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="17"/>
+      <c r="J12" s="17"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="13"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="23"/>
-      <c r="Q12" s="23"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C13" s="2"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="16"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="17"/>
+      <c r="J13" s="17"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="13"/>
       <c r="O13" s="2"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
